--- a/input/mapping/059. OCB_GOLD_TCKH_V_TB_AR_DTL_1_PHAT.xlsx
+++ b/input/mapping/059. OCB_GOLD_TCKH_V_TB_AR_DTL_1_PHAT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OCB\Zone_C\Code dev lại silver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="13_ncr:1_{18B2E4A2-A6C2-47DA-A270-A9F713991D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B8059F2-FCF9-46CB-82A0-F99CB00DB748}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{18B2E4A2-A6C2-47DA-A270-A9F713991D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{781B586B-1E75-4B7E-B762-95CA67ADA030}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -956,28 +956,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -985,15 +966,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -1002,7 +980,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -1013,18 +990,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -1035,15 +1017,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -1073,9 +1050,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -1084,8 +1060,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -1094,10 +1070,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -1106,9 +1082,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -1142,8 +1134,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>V_TB_AR_DTL_1
@@ -2913,7 +2904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3153,6 +3144,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3746,31 +3738,31 @@
     </row>
     <row r="25" spans="2:10" ht="26.25" customHeight="1">
       <c r="C25" s="13"/>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="90" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="21" customHeight="1">
       <c r="C26" s="14"/>
-      <c r="D26" s="89" t="s">
+      <c r="D26" s="90" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="22.5" customHeight="1">
       <c r="C27" s="15"/>
-      <c r="D27" s="89" t="s">
+      <c r="D27" s="90" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="23.25" customHeight="1">
       <c r="C28" s="16"/>
-      <c r="D28" s="89" t="s">
+      <c r="D28" s="90" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="20.25" customHeight="1">
       <c r="C29" s="17"/>
-      <c r="D29" s="89" t="s">
+      <c r="D29" s="90" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3851,7 +3843,7 @@
       <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="89" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3873,7 +3865,7 @@
       <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="89" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3987,11 +3979,11 @@
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="6" customHeight="1">
-      <c r="A8" s="90"/>
-      <c r="B8" s="90"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
     </row>
     <row r="9" spans="1:5" ht="25.5" customHeight="1">
       <c r="A9" s="80" t="s">
@@ -5335,11 +5327,11 @@
       <c r="E101" s="8"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="90"/>
-      <c r="B102" s="90"/>
-      <c r="C102" s="90"/>
-      <c r="D102" s="90"/>
-      <c r="E102" s="90"/>
+      <c r="A102" s="91"/>
+      <c r="B102" s="91"/>
+      <c r="C102" s="91"/>
+      <c r="D102" s="91"/>
+      <c r="E102" s="91"/>
     </row>
     <row r="103" spans="1:5" ht="18.75">
       <c r="A103" s="80" t="s">
@@ -6658,10 +6650,10 @@
       <c r="D193" s="7"/>
     </row>
     <row r="194" spans="1:4">
-      <c r="A194" s="90"/>
-      <c r="B194" s="90"/>
-      <c r="C194" s="90"/>
-      <c r="D194" s="90"/>
+      <c r="A194" s="91"/>
+      <c r="B194" s="91"/>
+      <c r="C194" s="91"/>
+      <c r="D194" s="91"/>
     </row>
     <row r="195" spans="1:4" ht="18.75">
       <c r="A195" s="80" t="s">
@@ -8613,6 +8605,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -8784,27 +8795,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36234F88-639F-4C47-9D16-0EF667429B42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BB095A-83D2-42D5-81BA-77562D80BA51}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8812,5 +8804,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BB095A-83D2-42D5-81BA-77562D80BA51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36234F88-639F-4C47-9D16-0EF667429B42}"/>
 </file>